--- a/output/yearly_total_coral_cover_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_45_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.272822581360028</v>
+        <v>1.259038843592403</v>
       </c>
       <c r="C3" t="n">
-        <v>4.618648655400253</v>
+        <v>4.695411508395312</v>
       </c>
       <c r="D3" t="n">
-        <v>6.041817819286627</v>
+        <v>6.061109161675077</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93328905604691</v>
+        <v>12.01555951366279</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.426822346277784</v>
+        <v>1.389482172040859</v>
       </c>
       <c r="C4" t="n">
-        <v>5.093797292604338</v>
+        <v>5.345443447478508</v>
       </c>
       <c r="D4" t="n">
-        <v>6.311318651427953</v>
+        <v>6.254552337224701</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83193829031008</v>
+        <v>12.98947795674407</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.638749143580762</v>
+        <v>1.565445013605302</v>
       </c>
       <c r="C5" t="n">
-        <v>5.693387668253853</v>
+        <v>6.231923345497138</v>
       </c>
       <c r="D5" t="n">
-        <v>6.549715066298988</v>
+        <v>6.471509152964243</v>
       </c>
       <c r="E5" t="n">
-        <v>13.8818518781336</v>
+        <v>14.26887751206668</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.879610173051596</v>
+        <v>1.765562459969251</v>
       </c>
       <c r="C6" t="n">
-        <v>6.437153511361559</v>
+        <v>7.300511195325137</v>
       </c>
       <c r="D6" t="n">
-        <v>6.833355307162146</v>
+        <v>6.712436611808887</v>
       </c>
       <c r="E6" t="n">
-        <v>15.1501189915753</v>
+        <v>15.77851026710328</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.148472853622196</v>
+        <v>1.979154501950366</v>
       </c>
       <c r="C7" t="n">
-        <v>7.33940734241701</v>
+        <v>8.508445992966831</v>
       </c>
       <c r="D7" t="n">
-        <v>7.149645528946796</v>
+        <v>6.97913323727543</v>
       </c>
       <c r="E7" t="n">
-        <v>16.637525724986</v>
+        <v>17.46673373219263</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.358339437261334</v>
+        <v>1.192260671483615</v>
       </c>
       <c r="C8" t="n">
-        <v>5.100540017873206</v>
+        <v>6.044283884657168</v>
       </c>
       <c r="D8" t="n">
-        <v>5.40448909906591</v>
+        <v>5.228042603317021</v>
       </c>
       <c r="E8" t="n">
-        <v>11.86336855420045</v>
+        <v>12.4645871594578</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.719738187072015</v>
+        <v>1.48787308104737</v>
       </c>
       <c r="C9" t="n">
-        <v>6.345489157566346</v>
+        <v>7.379374269234683</v>
       </c>
       <c r="D9" t="n">
-        <v>5.982862122900311</v>
+        <v>5.604568215587933</v>
       </c>
       <c r="E9" t="n">
-        <v>14.04808946753867</v>
+        <v>14.47181556586998</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.094264916294082</v>
+        <v>1.804435839116935</v>
       </c>
       <c r="C10" t="n">
-        <v>7.743946878130781</v>
+        <v>8.81536454966259</v>
       </c>
       <c r="D10" t="n">
-        <v>6.575471947282733</v>
+        <v>5.977334421855744</v>
       </c>
       <c r="E10" t="n">
-        <v>16.4136837417076</v>
+        <v>16.59713481063527</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.467838200537781</v>
+        <v>2.124376261036331</v>
       </c>
       <c r="C11" t="n">
-        <v>9.227684286518311</v>
+        <v>10.32827710911487</v>
       </c>
       <c r="D11" t="n">
-        <v>7.126604041493821</v>
+        <v>6.312207625564906</v>
       </c>
       <c r="E11" t="n">
-        <v>18.82212652854991</v>
+        <v>18.76486099571611</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.84243037946222</v>
+        <v>2.442027107320418</v>
       </c>
       <c r="C12" t="n">
-        <v>10.75951847897707</v>
+        <v>11.861730249644</v>
       </c>
       <c r="D12" t="n">
-        <v>7.653182088282287</v>
+        <v>6.683118086722605</v>
       </c>
       <c r="E12" t="n">
-        <v>21.25513094672158</v>
+        <v>20.98687544368702</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.216029183406724</v>
+        <v>2.754174816639942</v>
       </c>
       <c r="C13" t="n">
-        <v>12.36546906940574</v>
+        <v>13.41905752712632</v>
       </c>
       <c r="D13" t="n">
-        <v>8.143670186581769</v>
+        <v>7.068028085749167</v>
       </c>
       <c r="E13" t="n">
-        <v>23.72516843939423</v>
+        <v>23.24126042951542</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.856926695197629</v>
+        <v>1.588094721343726</v>
       </c>
       <c r="C14" t="n">
-        <v>8.617761712924416</v>
+        <v>9.485950660220999</v>
       </c>
       <c r="D14" t="n">
-        <v>6.241539569565436</v>
+        <v>5.393702252177891</v>
       </c>
       <c r="E14" t="n">
-        <v>16.71622797768748</v>
+        <v>16.46774763374261</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.914241126171558</v>
+        <v>1.622279176405599</v>
       </c>
       <c r="C15" t="n">
-        <v>9.332984550422303</v>
+        <v>9.997136872345271</v>
       </c>
       <c r="D15" t="n">
-        <v>6.291716694729492</v>
+        <v>5.329692301861</v>
       </c>
       <c r="E15" t="n">
-        <v>17.53894237132335</v>
+        <v>16.94910835061187</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.227958605063626</v>
+        <v>1.883217898717359</v>
       </c>
       <c r="C16" t="n">
-        <v>11.0712670355617</v>
+        <v>11.64815180405417</v>
       </c>
       <c r="D16" t="n">
-        <v>6.765645581477597</v>
+        <v>5.699143597923159</v>
       </c>
       <c r="E16" t="n">
-        <v>20.06487122210293</v>
+        <v>19.23051330069469</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.78970642988785</v>
+        <v>1.511704932476281</v>
       </c>
       <c r="C17" t="n">
-        <v>10.26755927748006</v>
+        <v>10.48075560893429</v>
       </c>
       <c r="D17" t="n">
-        <v>6.295545510776054</v>
+        <v>5.236946596240804</v>
       </c>
       <c r="E17" t="n">
-        <v>18.35281121814396</v>
+        <v>17.22940713765138</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.052598830131061</v>
+        <v>1.734620566202562</v>
       </c>
       <c r="C18" t="n">
-        <v>12.02893246862334</v>
+        <v>12.18211456291697</v>
       </c>
       <c r="D18" t="n">
-        <v>6.73630114259766</v>
+        <v>5.611856409538575</v>
       </c>
       <c r="E18" t="n">
-        <v>20.81783244135207</v>
+        <v>19.52859153865811</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.065813154230224</v>
+        <v>1.750308894516426</v>
       </c>
       <c r="C19" t="n">
-        <v>12.91315335593027</v>
+        <v>12.96938786442953</v>
       </c>
       <c r="D19" t="n">
-        <v>6.835997621963923</v>
+        <v>5.67627869389125</v>
       </c>
       <c r="E19" t="n">
-        <v>21.81496413212442</v>
+        <v>20.39597545283721</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.302227818889898</v>
+        <v>1.958949916622958</v>
       </c>
       <c r="C20" t="n">
-        <v>14.84487940871447</v>
+        <v>14.90299887280588</v>
       </c>
       <c r="D20" t="n">
-        <v>7.340046528278321</v>
+        <v>6.038357064694517</v>
       </c>
       <c r="E20" t="n">
-        <v>24.48715375588269</v>
+        <v>22.90030585412335</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.370303810633613</v>
+        <v>1.169330238097249</v>
       </c>
       <c r="C21" t="n">
-        <v>10.91803585388286</v>
+        <v>11.02878681239895</v>
       </c>
       <c r="D21" t="n">
-        <v>6.152976109165333</v>
+        <v>5.012420896279558</v>
       </c>
       <c r="E21" t="n">
-        <v>18.44131577368181</v>
+        <v>17.21053794677575</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_45_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259038843592403</v>
+        <v>1.275679467179387</v>
       </c>
       <c r="C3" t="n">
-        <v>4.695411508395312</v>
+        <v>4.62440169694714</v>
       </c>
       <c r="D3" t="n">
-        <v>6.061109161675077</v>
+        <v>6.090325973353462</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01555951366279</v>
+        <v>11.99040713747999</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.389482172040859</v>
+        <v>1.428658219022015</v>
       </c>
       <c r="C4" t="n">
-        <v>5.345443447478508</v>
+        <v>5.140526197085932</v>
       </c>
       <c r="D4" t="n">
-        <v>6.254552337224701</v>
+        <v>6.318719874654475</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98947795674407</v>
+        <v>12.88790429076242</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.565445013605302</v>
+        <v>1.631511398668721</v>
       </c>
       <c r="C5" t="n">
-        <v>6.231923345497138</v>
+        <v>5.795966120632073</v>
       </c>
       <c r="D5" t="n">
-        <v>6.471509152964243</v>
+        <v>6.722213345036231</v>
       </c>
       <c r="E5" t="n">
-        <v>14.26887751206668</v>
+        <v>14.14969086433702</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.765562459969251</v>
+        <v>1.864297120342844</v>
       </c>
       <c r="C6" t="n">
-        <v>7.300511195325137</v>
+        <v>6.634087919387527</v>
       </c>
       <c r="D6" t="n">
-        <v>6.712436611808887</v>
+        <v>7.098884488440191</v>
       </c>
       <c r="E6" t="n">
-        <v>15.77851026710328</v>
+        <v>15.59726952817056</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.979154501950366</v>
+        <v>2.134202734999687</v>
       </c>
       <c r="C7" t="n">
-        <v>8.508445992966831</v>
+        <v>7.623461874700675</v>
       </c>
       <c r="D7" t="n">
-        <v>6.97913323727543</v>
+        <v>7.528725692295709</v>
       </c>
       <c r="E7" t="n">
-        <v>17.46673373219263</v>
+        <v>17.28639030199607</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.192260671483615</v>
+        <v>1.351057216899562</v>
       </c>
       <c r="C8" t="n">
-        <v>6.044283884657168</v>
+        <v>5.315226070930348</v>
       </c>
       <c r="D8" t="n">
-        <v>5.228042603317021</v>
+        <v>5.754554408197981</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4645871594578</v>
+        <v>12.42083769602789</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.48787308104737</v>
+        <v>1.713099697483894</v>
       </c>
       <c r="C9" t="n">
-        <v>7.379374269234683</v>
+        <v>6.542198444227061</v>
       </c>
       <c r="D9" t="n">
-        <v>5.604568215587933</v>
+        <v>6.336098334788045</v>
       </c>
       <c r="E9" t="n">
-        <v>14.47181556586998</v>
+        <v>14.591396476499</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.804435839116935</v>
+        <v>2.087772853627109</v>
       </c>
       <c r="C10" t="n">
-        <v>8.81536454966259</v>
+        <v>7.927877409591439</v>
       </c>
       <c r="D10" t="n">
-        <v>5.977334421855744</v>
+        <v>6.892067167753622</v>
       </c>
       <c r="E10" t="n">
-        <v>16.59713481063527</v>
+        <v>16.90771743097217</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.124376261036331</v>
+        <v>2.471129566515972</v>
       </c>
       <c r="C11" t="n">
-        <v>10.32827710911487</v>
+        <v>9.468602566901851</v>
       </c>
       <c r="D11" t="n">
-        <v>6.312207625564906</v>
+        <v>7.472849412819239</v>
       </c>
       <c r="E11" t="n">
-        <v>18.76486099571611</v>
+        <v>19.41258154623706</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.442027107320418</v>
+        <v>2.84912806415847</v>
       </c>
       <c r="C12" t="n">
-        <v>11.861730249644</v>
+        <v>11.09715395420211</v>
       </c>
       <c r="D12" t="n">
-        <v>6.683118086722605</v>
+        <v>7.972433438536788</v>
       </c>
       <c r="E12" t="n">
-        <v>20.98687544368702</v>
+        <v>21.91871545689737</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.754174816639942</v>
+        <v>3.220317793875939</v>
       </c>
       <c r="C13" t="n">
-        <v>13.41905752712632</v>
+        <v>12.73299616009305</v>
       </c>
       <c r="D13" t="n">
-        <v>7.068028085749167</v>
+        <v>8.468230209943828</v>
       </c>
       <c r="E13" t="n">
-        <v>23.24126042951542</v>
+        <v>24.42154416391282</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.588094721343726</v>
+        <v>1.848012426043069</v>
       </c>
       <c r="C14" t="n">
-        <v>9.485950660220999</v>
+        <v>8.932549296814113</v>
       </c>
       <c r="D14" t="n">
-        <v>5.393702252177891</v>
+        <v>6.435120581888823</v>
       </c>
       <c r="E14" t="n">
-        <v>16.46774763374261</v>
+        <v>17.215682304746</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.622279176405599</v>
+        <v>1.90971526925498</v>
       </c>
       <c r="C15" t="n">
-        <v>9.997136872345271</v>
+        <v>9.68786671055344</v>
       </c>
       <c r="D15" t="n">
-        <v>5.329692301861</v>
+        <v>6.469511203968589</v>
       </c>
       <c r="E15" t="n">
-        <v>16.94910835061187</v>
+        <v>18.06709318377701</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.883217898717359</v>
+        <v>2.235773316789431</v>
       </c>
       <c r="C16" t="n">
-        <v>11.64815180405417</v>
+        <v>11.48702737083319</v>
       </c>
       <c r="D16" t="n">
-        <v>5.699143597923159</v>
+        <v>6.97214639358887</v>
       </c>
       <c r="E16" t="n">
-        <v>19.23051330069469</v>
+        <v>20.69494708121149</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.511704932476281</v>
+        <v>1.808644343102771</v>
       </c>
       <c r="C17" t="n">
-        <v>10.48075560893429</v>
+        <v>10.62650587310677</v>
       </c>
       <c r="D17" t="n">
-        <v>5.236946596240804</v>
+        <v>6.493603292630805</v>
       </c>
       <c r="E17" t="n">
-        <v>17.22940713765138</v>
+        <v>18.92875350884035</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.734620566202562</v>
+        <v>2.07530665453029</v>
       </c>
       <c r="C18" t="n">
-        <v>12.18211456291697</v>
+        <v>12.39938514734383</v>
       </c>
       <c r="D18" t="n">
-        <v>5.611856409538575</v>
+        <v>6.968690641669922</v>
       </c>
       <c r="E18" t="n">
-        <v>19.52859153865811</v>
+        <v>21.44338244354405</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.750308894516426</v>
+        <v>2.086459308450534</v>
       </c>
       <c r="C19" t="n">
-        <v>12.96938786442953</v>
+        <v>13.27056842513837</v>
       </c>
       <c r="D19" t="n">
-        <v>5.67627869389125</v>
+        <v>7.0719508652026</v>
       </c>
       <c r="E19" t="n">
-        <v>20.39597545283721</v>
+        <v>22.4289785987915</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.958949916622958</v>
+        <v>2.320517778620016</v>
       </c>
       <c r="C20" t="n">
-        <v>14.90299887280588</v>
+        <v>15.22235158352032</v>
       </c>
       <c r="D20" t="n">
-        <v>6.038357064694517</v>
+        <v>7.491490929135433</v>
       </c>
       <c r="E20" t="n">
-        <v>22.90030585412335</v>
+        <v>25.03436029127577</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.169330238097249</v>
+        <v>1.378039982543078</v>
       </c>
       <c r="C21" t="n">
-        <v>11.02878681239895</v>
+        <v>11.17414437748973</v>
       </c>
       <c r="D21" t="n">
-        <v>5.012420896279558</v>
+        <v>6.254832433480939</v>
       </c>
       <c r="E21" t="n">
-        <v>17.21053794677575</v>
+        <v>18.80701679351375</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_45_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.275679467179387</v>
+        <v>2.607531241840101</v>
       </c>
       <c r="C3" t="n">
-        <v>4.62440169694714</v>
+        <v>7.733557629928076</v>
       </c>
       <c r="D3" t="n">
-        <v>6.090325973353462</v>
+        <v>8.205464752106348</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99040713747999</v>
+        <v>18.54655362387452</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.428658219022015</v>
+        <v>1.110547831848767</v>
       </c>
       <c r="C4" t="n">
-        <v>5.140526197085932</v>
+        <v>4.634931993481921</v>
       </c>
       <c r="D4" t="n">
-        <v>6.318719874654475</v>
+        <v>5.845914534961708</v>
       </c>
       <c r="E4" t="n">
-        <v>12.88790429076242</v>
+        <v>11.5913943602924</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.631511398668721</v>
+        <v>1.237127851589922</v>
       </c>
       <c r="C5" t="n">
-        <v>5.795966120632073</v>
+        <v>5.460023556915401</v>
       </c>
       <c r="D5" t="n">
-        <v>6.722213345036231</v>
+        <v>6.176044071196872</v>
       </c>
       <c r="E5" t="n">
-        <v>14.14969086433702</v>
+        <v>12.8731954797022</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.864297120342844</v>
+        <v>1.372422306916198</v>
       </c>
       <c r="C6" t="n">
-        <v>6.634087919387527</v>
+        <v>6.499971320299275</v>
       </c>
       <c r="D6" t="n">
-        <v>7.098884488440191</v>
+        <v>6.540384860524576</v>
       </c>
       <c r="E6" t="n">
-        <v>15.59726952817056</v>
+        <v>14.41277848774005</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.134202734999687</v>
+        <v>1.508586598907341</v>
       </c>
       <c r="C7" t="n">
-        <v>7.623461874700675</v>
+        <v>7.690405378331439</v>
       </c>
       <c r="D7" t="n">
-        <v>7.528725692295709</v>
+        <v>6.908443098163104</v>
       </c>
       <c r="E7" t="n">
-        <v>17.28639030199607</v>
+        <v>16.10743507540188</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.351057216899562</v>
+        <v>1.641311933442563</v>
       </c>
       <c r="C8" t="n">
-        <v>5.315226070930348</v>
+        <v>9.043744767777811</v>
       </c>
       <c r="D8" t="n">
-        <v>5.754554408197981</v>
+        <v>7.369827012149551</v>
       </c>
       <c r="E8" t="n">
-        <v>12.42083769602789</v>
+        <v>18.05488371336993</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.713099697483894</v>
+        <v>1.754843025178918</v>
       </c>
       <c r="C9" t="n">
-        <v>6.542198444227061</v>
+        <v>10.52466354568006</v>
       </c>
       <c r="D9" t="n">
-        <v>6.336098334788045</v>
+        <v>7.754452570346307</v>
       </c>
       <c r="E9" t="n">
-        <v>14.591396476499</v>
+        <v>20.03395914120529</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.087772853627109</v>
+        <v>1.083103337233251</v>
       </c>
       <c r="C10" t="n">
-        <v>7.927877409591439</v>
+        <v>7.591796092078329</v>
       </c>
       <c r="D10" t="n">
-        <v>6.892067167753622</v>
+        <v>6.093305483701211</v>
       </c>
       <c r="E10" t="n">
-        <v>16.90771743097217</v>
+        <v>14.76820491301279</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.471129566515972</v>
+        <v>1.00513293456197</v>
       </c>
       <c r="C11" t="n">
-        <v>9.468602566901851</v>
+        <v>8.229176154106487</v>
       </c>
       <c r="D11" t="n">
-        <v>7.472849412819239</v>
+        <v>5.961829831148478</v>
       </c>
       <c r="E11" t="n">
-        <v>19.41258154623706</v>
+        <v>15.19613891981693</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.84912806415847</v>
+        <v>1.069781020886622</v>
       </c>
       <c r="C12" t="n">
-        <v>11.09715395420211</v>
+        <v>9.856737133160935</v>
       </c>
       <c r="D12" t="n">
-        <v>7.972433438536788</v>
+        <v>6.345467381537004</v>
       </c>
       <c r="E12" t="n">
-        <v>21.91871545689737</v>
+        <v>17.27198553558456</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.220317793875939</v>
+        <v>0.831530488020006</v>
       </c>
       <c r="C13" t="n">
-        <v>12.73299616009305</v>
+        <v>9.465962276962534</v>
       </c>
       <c r="D13" t="n">
-        <v>8.468230209943828</v>
+        <v>5.786430786307744</v>
       </c>
       <c r="E13" t="n">
-        <v>24.42154416391282</v>
+        <v>16.08392355129028</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.848012426043069</v>
+        <v>0.8890412685347842</v>
       </c>
       <c r="C14" t="n">
-        <v>8.932549296814113</v>
+        <v>11.22494000370746</v>
       </c>
       <c r="D14" t="n">
-        <v>6.435120581888823</v>
+        <v>6.173435731321836</v>
       </c>
       <c r="E14" t="n">
-        <v>17.215682304746</v>
+        <v>18.28741700356408</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.90971526925498</v>
+        <v>0.8498793526123789</v>
       </c>
       <c r="C15" t="n">
-        <v>9.68786671055344</v>
+        <v>12.26115507058588</v>
       </c>
       <c r="D15" t="n">
-        <v>6.469511203968589</v>
+        <v>6.205067642352668</v>
       </c>
       <c r="E15" t="n">
-        <v>18.06709318377701</v>
+        <v>19.31610206555093</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.235773316789431</v>
+        <v>0.9163142197587606</v>
       </c>
       <c r="C16" t="n">
-        <v>11.48702737083319</v>
+        <v>14.33051233402844</v>
       </c>
       <c r="D16" t="n">
-        <v>6.97214639358887</v>
+        <v>6.609950213061095</v>
       </c>
       <c r="E16" t="n">
-        <v>20.69494708121149</v>
+        <v>21.85677676684829</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.808644343102771</v>
+        <v>0.5447325311783853</v>
       </c>
       <c r="C17" t="n">
-        <v>10.62650587310677</v>
+        <v>10.72744917205743</v>
       </c>
       <c r="D17" t="n">
-        <v>6.493603292630805</v>
+        <v>5.491101441916218</v>
       </c>
       <c r="E17" t="n">
-        <v>18.92875350884035</v>
+        <v>16.76328314515203</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.07530665453029</v>
+        <v>0.4215919166347079</v>
       </c>
       <c r="C18" t="n">
-        <v>12.39938514734383</v>
+        <v>9.74855835362998</v>
       </c>
       <c r="D18" t="n">
-        <v>6.968690641669922</v>
+        <v>4.995809725123702</v>
       </c>
       <c r="E18" t="n">
-        <v>21.44338244354405</v>
+        <v>15.16595999538839</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.086459308450534</v>
+        <v>0.4836481890201487</v>
       </c>
       <c r="C19" t="n">
-        <v>13.27056842513837</v>
+        <v>12.16459036639616</v>
       </c>
       <c r="D19" t="n">
-        <v>7.0719508652026</v>
+        <v>5.476178876811666</v>
       </c>
       <c r="E19" t="n">
-        <v>22.4289785987915</v>
+        <v>18.12441743222798</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.320517778620016</v>
+        <v>0.5413455015987337</v>
       </c>
       <c r="C20" t="n">
-        <v>15.22235158352032</v>
+        <v>14.66567118278125</v>
       </c>
       <c r="D20" t="n">
-        <v>7.491490929135433</v>
+        <v>5.9043190506337</v>
       </c>
       <c r="E20" t="n">
-        <v>25.03436029127577</v>
+        <v>21.11133573501369</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.378039982543078</v>
+        <v>0.5903739819488194</v>
       </c>
       <c r="C21" t="n">
-        <v>11.17414437748973</v>
+        <v>17.14622365467055</v>
       </c>
       <c r="D21" t="n">
-        <v>6.254832433480939</v>
+        <v>6.330034307626245</v>
       </c>
       <c r="E21" t="n">
-        <v>18.80701679351375</v>
+        <v>24.06663194424561</v>
       </c>
     </row>
   </sheetData>
